--- a/artfynd/A 42489-2025 artfynd.xlsx
+++ b/artfynd/A 42489-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1497,51 +1497,55 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>93561579</v>
+        <v>137427835</v>
       </c>
       <c r="B9" t="n">
-        <v>91909</v>
+        <v>93491</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>789</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bässeravinen, Hls</t>
+          <t>Bässe södra bäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599758</v>
+        <v>599724</v>
       </c>
       <c r="R9" t="n">
-        <v>6820312</v>
+        <v>6820328</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1565,12 +1569,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Tillsammans med Fjällig taggsvamp och Koppartaggsvamp inom 5 meter, återfynd känd lokal</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,47 +1592,37 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Låga</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies # Låga</t>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrblandsko ca 120-årig bäckravin</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Alf Bjarne Roland Pallin</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93561579</t>
+          <t>https://artportalen.se/Sighting/137427835</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>93961538</v>
+        <v>93561579</v>
       </c>
       <c r="B10" t="n">
         <v>91909</v>
@@ -1661,10 +1660,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599751</v>
+        <v>599758</v>
       </c>
       <c r="R10" t="n">
-        <v>6820328</v>
+        <v>6820312</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1691,12 +1690,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-05-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-05-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,75 +1708,88 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies # Låga</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Björn Bråvander, Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93961538</t>
+          <t>https://artportalen.se/Sighting/93561579</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6928476</v>
+        <v>93961538</v>
       </c>
       <c r="B11" t="n">
-        <v>93205</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2058</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>bässe, Hls</t>
+          <t>Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599747</v>
+        <v>599751</v>
       </c>
       <c r="R11" t="n">
-        <v>6820337</v>
+        <v>6820328</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1804,12 +1816,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2013-08-31</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2013-08-31</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,37 +1834,27 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrblandskog örtrik bäckravin</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6928476</t>
+          <t>https://artportalen.se/Sighting/93961538</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>93561698</v>
+        <v>6928476</v>
       </c>
       <c r="B12" t="n">
         <v>93205</v>
@@ -1880,23 +1882,30 @@
           <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bässeravinen, Hls</t>
+          <t>bässe, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599729</v>
+        <v>599747</v>
       </c>
       <c r="R12" t="n">
-        <v>6820311</v>
+        <v>6820337</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,17 +1929,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
+          <t>2013-08-31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Fjolårsex</t>
+          <t>2013-08-31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,27 +1947,37 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrblandskog örtrik bäckravin</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Alf Bjarne Roland Pallin</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93561698</t>
+          <t>https://artportalen.se/Sighting/6928476</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95488200</v>
+        <v>93561698</v>
       </c>
       <c r="B13" t="n">
         <v>93205</v>
@@ -2001,13 +2015,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599727</v>
+        <v>599729</v>
       </c>
       <c r="R13" t="n">
-        <v>6820334</v>
+        <v>6820311</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2031,12 +2045,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2021-05-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2021-05-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Fjolårsex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,24 +2071,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Max Rosendahl, Andreas Thomas Nilsson</t>
+          <t>Björn Bråvander, Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95488200</t>
+          <t>https://artportalen.se/Sighting/93561698</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95540382</v>
+        <v>95488200</v>
       </c>
       <c r="B14" t="n">
         <v>93205</v>
@@ -2097,16 +2116,8 @@
           <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2115,13 +2126,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599730</v>
+        <v>599727</v>
       </c>
       <c r="R14" t="n">
-        <v>6820323</v>
+        <v>6820334</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2145,17 +2156,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Återfynd tillsammans med raggtaggsvamp</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,47 +2174,27 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Rikare barrblandskog vid bäckravin</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Marken</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Marken</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Max Rosendahl, Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95540382</t>
+          <t>https://artportalen.se/Sighting/95488200</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128316972</v>
+        <v>95540382</v>
       </c>
       <c r="B15" t="n">
         <v>93205</v>
@@ -2236,23 +2222,31 @@
           <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bässe vid bäcken, Hls</t>
+          <t>Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599782</v>
+        <v>599730</v>
       </c>
       <c r="R15" t="n">
-        <v>6820318</v>
+        <v>6820323</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2276,17 +2270,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Återfynd 4 fruktkroppar</t>
+          <t>Återfynd tillsammans med raggtaggsvamp</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,6 +2293,26 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Rikare barrblandskog vid bäckravin</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Marken</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Marken</t>
+        </is>
+      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
@@ -2313,62 +2327,54 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128316972</t>
+          <t>https://artportalen.se/Sighting/95540382</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>85678930</v>
+        <v>128316972</v>
       </c>
       <c r="B16" t="n">
-        <v>92281</v>
+        <v>93205</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2062</v>
+        <v>2058</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>bässe, Hls</t>
+          <t>Bässe vid bäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599747</v>
+        <v>599782</v>
       </c>
       <c r="R16" t="n">
-        <v>6820337</v>
+        <v>6820318</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2395,17 +2401,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-05-22</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-05-22</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Två små fruktkroppar och flera på gång, strax efter där raggtaggsvampen växer</t>
+          <t>Återfynd 4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2418,21 +2424,6 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Barrblandskog i bäckravin med lågor och död ved</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Substratet ullticka på granlåga.</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
@@ -2447,45 +2438,41 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85678930</t>
+          <t>https://artportalen.se/Sighting/128316972</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119358810</v>
+        <v>137427802</v>
       </c>
       <c r="B17" t="n">
-        <v>93193</v>
+        <v>93489</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4363</v>
+        <v>2058</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -2495,17 +2482,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>bässe, Hls</t>
+          <t>Bässe södra bäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599747</v>
+        <v>599724</v>
       </c>
       <c r="R17" t="n">
-        <v>6820337</v>
+        <v>6820328</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2529,17 +2516,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Växte i en liten grupp</t>
+          <t>Tillsammans med Raggtaggsvamp och Fjällig taggsvamp inom 5 meter. Återfynd känd lokal</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2559,7 +2546,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
+          <t>Barrblandskog ca 120-årig vid bäckravin</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2576,63 +2563,65 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119358810</t>
+          <t>https://artportalen.se/Sighting/137427802</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>62130463</v>
+        <v>85678930</v>
       </c>
       <c r="B18" t="n">
-        <v>93209</v>
+        <v>92281</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bässeravinen, Hls</t>
+          <t>bässe, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599744</v>
+        <v>599747</v>
       </c>
       <c r="R18" t="n">
-        <v>6820322</v>
+        <v>6820337</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2656,12 +2645,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2020-05-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2020-05-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två små fruktkroppar och flera på gång, strax efter där raggtaggsvampen växer</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2670,76 +2664,95 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>gammal granskog i bäckmiljö</t>
+          <t>Barrblandskog i bäckravin med lågor och död ved</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Substratet ullticka på granlåga.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62130463</t>
+          <t>https://artportalen.se/Sighting/85678930</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128317134</v>
+        <v>119358810</v>
       </c>
       <c r="B19" t="n">
-        <v>89138</v>
+        <v>93193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4404</v>
+        <v>4363</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sotvaxskivling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hygrophorus camarophyllus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bässe vid bäcken, Hls</t>
+          <t>bässe, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599782</v>
+        <v>599747</v>
       </c>
       <c r="R19" t="n">
-        <v>6820318</v>
+        <v>6820337</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2766,12 +2779,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Växte i en liten grupp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2791,7 +2809,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkpåverkad barrblandskog främst gran med inslag av äldre tall och björk</t>
+          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2808,16 +2826,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317134</t>
+          <t>https://artportalen.se/Sighting/119358810</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>62130462</v>
+        <v>62130463</v>
       </c>
       <c r="B20" t="n">
-        <v>93233</v>
+        <v>93209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,21 +2843,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2858,10 +2876,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599726</v>
+        <v>599744</v>
       </c>
       <c r="R20" t="n">
-        <v>6820332</v>
+        <v>6820322</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2902,7 +2920,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2925,7 +2942,365 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/62130463</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128317134</v>
+      </c>
+      <c r="B21" t="n">
+        <v>89138</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4404</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sotvaxskivling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hygrophorus camarophyllus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bässe vid bäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>599782</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6820318</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkpåverkad barrblandskog främst gran med inslag av äldre tall och björk</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128317134</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>62130462</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>599726</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6820332</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2016-09-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2016-09-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>gammal granskog i bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/62130462</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137427713</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93517</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bässe södra bäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>599724</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6820328</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Tillsammans med Raggtaggsvamp och Koppartaggsvamp inom 5 meter</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Barrblandskog vid bäckravin</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137427713</t>
         </is>
       </c>
     </row>
@@ -2950,6 +3325,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42489-2025 artfynd.xlsx
+++ b/artfynd/A 42489-2025 artfynd.xlsx
@@ -1500,7 +1500,7 @@
         <v>137427835</v>
       </c>
       <c r="B9" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>137427802</v>
       </c>
       <c r="B17" t="n">
-        <v>93489</v>
+        <v>93490</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>137427713</v>
       </c>
       <c r="B23" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 42489-2025 artfynd.xlsx
+++ b/artfynd/A 42489-2025 artfynd.xlsx
@@ -1500,7 +1500,7 @@
         <v>137427835</v>
       </c>
       <c r="B9" t="n">
-        <v>93492</v>
+        <v>93495</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>137427802</v>
       </c>
       <c r="B17" t="n">
-        <v>93490</v>
+        <v>93493</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>137427713</v>
       </c>
       <c r="B23" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 42489-2025 artfynd.xlsx
+++ b/artfynd/A 42489-2025 artfynd.xlsx
@@ -1500,7 +1500,7 @@
         <v>137427835</v>
       </c>
       <c r="B9" t="n">
-        <v>93495</v>
+        <v>93499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>137427802</v>
       </c>
       <c r="B17" t="n">
-        <v>93493</v>
+        <v>93497</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>137427713</v>
       </c>
       <c r="B23" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
